--- a/Docs/玩法数值表.xlsx
+++ b/Docs/玩法数值表.xlsx
@@ -359,8 +359,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TemplateTable4" displayName="TemplateTable4" ref="A1:L11" headerRowCount="1">
-  <autoFilter ref="A1:L11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="WeaponMainTable" displayName="WeaponMainTable" ref="A1:L9" headerRowCount="1">
+  <autoFilter ref="A1:L9"/>
   <tableColumns count="12">
     <tableColumn id="1" name="武器ID"/>
     <tableColumn id="2" name="名称"/>
@@ -380,8 +380,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TemplateTable5" displayName="TemplateTable5" ref="A1:W11" headerRowCount="1">
-  <autoFilter ref="A1:W11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="WeaponLevelTable" displayName="WeaponLevelTable" ref="A1:W33" headerRowCount="1">
+  <autoFilter ref="A1:W33"/>
   <tableColumns count="23">
     <tableColumn id="1" name="武器ID"/>
     <tableColumn id="2" name="等级"/>
@@ -11558,10 +11558,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -11572,7 +11572,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="33" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -11638,144 +11638,436 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_IronHammer</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>铁锤</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>正常武器</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>重型</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>低频高伤近战扫掠</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>重型近战基准，单次命中强，攻速成长保守。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_RapidSMG</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>冲锋枪</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>正常武器</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>快速</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>远程</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>高攻速低单发远程</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>快速武器，击退和暴击收益率保守。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_HuntingRifle</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>猎枪</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>正常武器</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>精准</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>远程</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>低频远程精准单体</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>精准远程，暴击成长明显但攻速保守。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_FireWand</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>火焰法杖</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>强力武器</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>成长</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>魔法</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>魔法范围持续输出</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3+</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>强力武器，范围和魔法收益潜力高。成长标签暂按魔法构筑承载处理。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_SummonOrb</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>召唤法球</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>强力武器</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>成长</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>召唤</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>召唤持续输出</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>召唤构筑入口，基础较慢但收益率高。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_DaggerRing</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>匕首环</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>正常武器</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>快速</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>近战/精准</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>近身高频暴击</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2+</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>近战快速精准混合，范围短，安全性低。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_ArcaneBolt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>奥术弹</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>正常武器</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>精准</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>魔法</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>魔法单体弹体</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>魔法精准单体，介于猎枪和法杖之间。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_GreatAxe</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>巨斧</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>强力武器</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>重型</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>大范围低频近战</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>强力重型，范围和单次伤害高，攻速短板明显。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11791,10 +12083,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:W33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -11806,17 +12098,17 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -11937,254 +12229,2564 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_IronHammer</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>AS 60; CritChance 60; CritPercent 70; Range 80; Knockback 70; Melee 80</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O2" s="2">
+        <f>C2*(D2/100)*(1+E2/100*MAX(0,F2/100-1))</f>
+        <v/>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" s="2">
+        <f>O2*P2*Q2*R2</f>
+        <v/>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" s="2">
+        <f>ROUND(VLOOKUP(A2,'04_武器主表'!$A:$I,9,FALSE)*T2,0)</f>
+        <v/>
+      </c>
       <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>Lv1 重击入口。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr"/>
-      <c r="U3" s="2" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_IronHammer</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>AS 60; CritChance 60; CritPercent 75; Range 85; Knockback 75; Melee 90</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O3" s="2">
+        <f>C3*(D3/100)*(1+E3/100*MAX(0,F3/100-1))</f>
+        <v/>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S3" s="2">
+        <f>O3*P3*Q3*R3</f>
+        <v/>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U3" s="2">
+        <f>ROUND(VLOOKUP(A3,'04_武器主表'!$A:$I,9,FALSE)*T3,0)</f>
+        <v/>
+      </c>
       <c r="V3" s="2" t="inlineStr"/>
-      <c r="W3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>提高基础攻击和范围。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr"/>
-      <c r="U4" s="2" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_IronHammer</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>AS 65; CritChance 65; CritPercent 80; Range 90; Knockback 80; Melee 100</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O4" s="2">
+        <f>C4*(D4/100)*(1+E4/100*MAX(0,F4/100-1))</f>
+        <v/>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="S4" s="2">
+        <f>O4*P4*Q4*R4</f>
+        <v/>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U4" s="2">
+        <f>ROUND(VLOOKUP(A4,'04_武器主表'!$A:$I,9,FALSE)*T4,0)</f>
+        <v/>
+      </c>
       <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>中段成型，少量暴击。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr"/>
-      <c r="U5" s="2" t="inlineStr"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_IronHammer</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>205</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>AS 65; CritChance 70; CritPercent 85; Range 95; Knockback 85; Melee 110</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O5" s="2">
+        <f>C5*(D5/100)*(1+E5/100*MAX(0,F5/100-1))</f>
+        <v/>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="S5" s="2">
+        <f>O5*P5*Q5*R5</f>
+        <v/>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="U5" s="2">
+        <f>ROUND(VLOOKUP(A5,'04_武器主表'!$A:$I,9,FALSE)*T5,0)</f>
+        <v/>
+      </c>
       <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>完整重型形态。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
-      <c r="U6" s="2" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_RapidSMG</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>AS 80; CritChance 40; CritPercent 40; Range 70; Knockback 25; Ranged 70</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O6" s="2">
+        <f>C6*(D6/100)*(1+E6/100*MAX(0,F6/100-1))</f>
+        <v/>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="2">
+        <f>O6*P6*Q6*R6</f>
+        <v/>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="2">
+        <f>ROUND(VLOOKUP(A6,'04_武器主表'!$A:$I,9,FALSE)*T6,0)</f>
+        <v/>
+      </c>
       <c r="V6" s="2" t="inlineStr"/>
-      <c r="W6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>高频基础入口。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr"/>
-      <c r="U7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_RapidSMG</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>680</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>AS 82; CritChance 40; CritPercent 40; Range 75; Knockback 25; Ranged 80</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" s="2">
+        <f>C7*(D7/100)*(1+E7/100*MAX(0,F7/100-1))</f>
+        <v/>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="2">
+        <f>O7*P7*Q7*R7</f>
+        <v/>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U7" s="2">
+        <f>ROUND(VLOOKUP(A7,'04_武器主表'!$A:$I,9,FALSE)*T7,0)</f>
+        <v/>
+      </c>
       <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>主加攻速。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr"/>
-      <c r="U8" s="2" t="inlineStr"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_RapidSMG</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>295</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>AS 84; CritChance 45; CritPercent 45; Range 80; Knockback 30; Ranged 90</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" s="2">
+        <f>C8*(D8/100)*(1+E8/100*MAX(0,F8/100-1))</f>
+        <v/>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="2">
+        <f>O8*P8*Q8*R8</f>
+        <v/>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U8" s="2">
+        <f>ROUND(VLOOKUP(A8,'04_武器主表'!$A:$I,9,FALSE)*T8,0)</f>
+        <v/>
+      </c>
       <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>提高单发和攻速。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr"/>
-      <c r="U9" s="2" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_RapidSMG</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>AS 85; CritChance 45; CritPercent 45; Range 85; Knockback 30; Ranged 100</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" s="2">
+        <f>C9*(D9/100)*(1+E9/100*MAX(0,F9/100-1))</f>
+        <v/>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" s="2">
+        <f>O9*P9*Q9*R9</f>
+        <v/>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="U9" s="2">
+        <f>ROUND(VLOOKUP(A9,'04_武器主表'!$A:$I,9,FALSE)*T9,0)</f>
+        <v/>
+      </c>
       <c r="V9" s="2" t="inlineStr"/>
-      <c r="W9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>完整快速形态。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr"/>
-      <c r="U10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_HuntingRifle</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>AS 70; CritChance 80; CritPercent 90; Range 90; Knockback 55; Ranged 85</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" s="2">
+        <f>C10*(D10/100)*(1+E10/100*MAX(0,F10/100-1))</f>
+        <v/>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" s="2">
+        <f>O10*P10*Q10*R10</f>
+        <v/>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" s="2">
+        <f>ROUND(VLOOKUP(A10,'04_武器主表'!$A:$I,9,FALSE)*T10,0)</f>
+        <v/>
+      </c>
       <c r="V10" s="2" t="inlineStr"/>
-      <c r="W10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>精准入门。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr"/>
-      <c r="U11" s="2" t="inlineStr"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_HuntingRifle</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>AS 70; CritChance 85; CritPercent 95; Range 95; Knockback 60; Ranged 95</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O11" s="2">
+        <f>C11*(D11/100)*(1+E11/100*MAX(0,F11/100-1))</f>
+        <v/>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S11" s="2">
+        <f>O11*P11*Q11*R11</f>
+        <v/>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U11" s="2">
+        <f>ROUND(VLOOKUP(A11,'04_武器主表'!$A:$I,9,FALSE)*T11,0)</f>
+        <v/>
+      </c>
       <c r="V11" s="2" t="inlineStr"/>
-      <c r="W11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>提高暴击和攻击。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_HuntingRifle</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>205</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>AS 75; CritChance 90; CritPercent 100; Range 100; Knockback 65; Ranged 105</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" s="2">
+        <f>C12*(D12/100)*(1+E12/100*MAX(0,F12/100-1))</f>
+        <v/>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="S12" s="2">
+        <f>O12*P12*Q12*R12</f>
+        <v/>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U12" s="2">
+        <f>ROUND(VLOOKUP(A12,'04_武器主表'!$A:$I,9,FALSE)*T12,0)</f>
+        <v/>
+      </c>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>暴击成型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_HuntingRifle</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>225</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1020</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>AS 75; CritChance 95; CritPercent 110; Range 105; Knockback 70; Ranged 120</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O13" s="2">
+        <f>C13*(D13/100)*(1+E13/100*MAX(0,F13/100-1))</f>
+        <v/>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="S13" s="2">
+        <f>O13*P13*Q13*R13</f>
+        <v/>
+      </c>
+      <c r="T13" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="U13" s="2">
+        <f>ROUND(VLOOKUP(A13,'04_武器主表'!$A:$I,9,FALSE)*T13,0)</f>
+        <v/>
+      </c>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>后期精准核心。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_FireWand</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>620</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>AS 70; CritChance 60; CritPercent 70; Range 80; Knockback 30; Magic 90</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Damage +1</t>
+        </is>
+      </c>
+      <c r="O14" s="2">
+        <f>C14*(D14/100)*(1+E14/100*MAX(0,F14/100-1))</f>
+        <v/>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="S14" s="2">
+        <f>O14*P14*Q14*R14</f>
+        <v/>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" s="2">
+        <f>ROUND(VLOOKUP(A14,'04_武器主表'!$A:$I,9,FALSE)*T14,0)</f>
+        <v/>
+      </c>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>范围持续入口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_FireWand</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>660</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>AS 75; CritChance 65; CritPercent 75; Range 85; Knockback 30; Magic 105</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Damage +1</t>
+        </is>
+      </c>
+      <c r="O15" s="2">
+        <f>C15*(D15/100)*(1+E15/100*MAX(0,F15/100-1))</f>
+        <v/>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S15" s="2">
+        <f>O15*P15*Q15*R15</f>
+        <v/>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U15" s="2">
+        <f>ROUND(VLOOKUP(A15,'04_武器主表'!$A:$I,9,FALSE)*T15,0)</f>
+        <v/>
+      </c>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>提高范围稳定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_FireWand</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>AS 80; CritChance 70; CritPercent 80; Range 90; Knockback 35; Magic 120</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Damage +2</t>
+        </is>
+      </c>
+      <c r="O16" s="2">
+        <f>C16*(D16/100)*(1+E16/100*MAX(0,F16/100-1))</f>
+        <v/>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S16" s="2">
+        <f>O16*P16*Q16*R16</f>
+        <v/>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U16" s="2">
+        <f>ROUND(VLOOKUP(A16,'04_武器主表'!$A:$I,9,FALSE)*T16,0)</f>
+        <v/>
+      </c>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>魔法构筑承载。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_FireWand</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>760</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>AS 85; CritChance 75; CritPercent 90; Range 100; Knockback 35; Magic 140</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Damage +3</t>
+        </is>
+      </c>
+      <c r="O17" s="2">
+        <f>C17*(D17/100)*(1+E17/100*MAX(0,F17/100-1))</f>
+        <v/>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S17" s="2">
+        <f>O17*P17*Q17*R17</f>
+        <v/>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="U17" s="2">
+        <f>ROUND(VLOOKUP(A17,'04_武器主表'!$A:$I,9,FALSE)*T17,0)</f>
+        <v/>
+      </c>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>完整范围形态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_SummonOrb</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>AS 60; CritChance 40; CritPercent 50; Range 80; Knockback 20; Summon 100</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>SummonAttack +1</t>
+        </is>
+      </c>
+      <c r="O18" s="2">
+        <f>C18*(D18/100)*(1+E18/100*MAX(0,F18/100-1))</f>
+        <v/>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" s="2">
+        <f>O18*P18*Q18*R18</f>
+        <v/>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" s="2">
+        <f>ROUND(VLOOKUP(A18,'04_武器主表'!$A:$I,9,FALSE)*T18,0)</f>
+        <v/>
+      </c>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>召唤入口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_SummonOrb</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>730</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>AS 65; CritChance 45; CritPercent 55; Range 85; Knockback 20; Summon 115</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>SummonAttack +2</t>
+        </is>
+      </c>
+      <c r="O19" s="2">
+        <f>C19*(D19/100)*(1+E19/100*MAX(0,F19/100-1))</f>
+        <v/>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S19" s="2">
+        <f>O19*P19*Q19*R19</f>
+        <v/>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U19" s="2">
+        <f>ROUND(VLOOKUP(A19,'04_武器主表'!$A:$I,9,FALSE)*T19,0)</f>
+        <v/>
+      </c>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>提高召唤收益。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_SummonOrb</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>760</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>AS 70; CritChance 50; CritPercent 60; Range 90; Knockback 25; Summon 135</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>SummonAttack +3</t>
+        </is>
+      </c>
+      <c r="O20" s="2">
+        <f>C20*(D20/100)*(1+E20/100*MAX(0,F20/100-1))</f>
+        <v/>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="S20" s="2">
+        <f>O20*P20*Q20*R20</f>
+        <v/>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U20" s="2">
+        <f>ROUND(VLOOKUP(A20,'04_武器主表'!$A:$I,9,FALSE)*T20,0)</f>
+        <v/>
+      </c>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>中期召唤成型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_SummonOrb</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>820</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>AS 75; CritChance 55; CritPercent 65; Range 100; Knockback 25; Summon 160</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>SummonAttack +4</t>
+        </is>
+      </c>
+      <c r="O21" s="2">
+        <f>C21*(D21/100)*(1+E21/100*MAX(0,F21/100-1))</f>
+        <v/>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="S21" s="2">
+        <f>O21*P21*Q21*R21</f>
+        <v/>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="U21" s="2">
+        <f>ROUND(VLOOKUP(A21,'04_武器主表'!$A:$I,9,FALSE)*T21,0)</f>
+        <v/>
+      </c>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>后期召唤核心。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_DaggerRing</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>AS 75; CritChance 70; CritPercent 75; Range 60; Knockback 35; Melee 80</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O22" s="2">
+        <f>C22*(D22/100)*(1+E22/100*MAX(0,F22/100-1))</f>
+        <v/>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="S22" s="2">
+        <f>O22*P22*Q22*R22</f>
+        <v/>
+      </c>
+      <c r="T22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="2">
+        <f>ROUND(VLOOKUP(A22,'04_武器主表'!$A:$I,9,FALSE)*T22,0)</f>
+        <v/>
+      </c>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>近身风险换频率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_DaggerRing</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>AS 78; CritChance 75; CritPercent 80; Range 62; Knockback 35; Melee 90</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O23" s="2">
+        <f>C23*(D23/100)*(1+E23/100*MAX(0,F23/100-1))</f>
+        <v/>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="S23" s="2">
+        <f>O23*P23*Q23*R23</f>
+        <v/>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U23" s="2">
+        <f>ROUND(VLOOKUP(A23,'04_武器主表'!$A:$I,9,FALSE)*T23,0)</f>
+        <v/>
+      </c>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>提高攻速暴击。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_DaggerRing</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>185</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>AS 80; CritChance 80; CritPercent 85; Range 65; Knockback 40; Melee 105</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O24" s="2">
+        <f>C24*(D24/100)*(1+E24/100*MAX(0,F24/100-1))</f>
+        <v/>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="S24" s="2">
+        <f>O24*P24*Q24*R24</f>
+        <v/>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U24" s="2">
+        <f>ROUND(VLOOKUP(A24,'04_武器主表'!$A:$I,9,FALSE)*T24,0)</f>
+        <v/>
+      </c>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>高频暴击成型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_DaggerRing</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>280</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>AS 82; CritChance 85; CritPercent 95; Range 70; Knockback 40; Melee 120</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" s="2">
+        <f>C25*(D25/100)*(1+E25/100*MAX(0,F25/100-1))</f>
+        <v/>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S25" s="2">
+        <f>O25*P25*Q25*R25</f>
+        <v/>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="U25" s="2">
+        <f>ROUND(VLOOKUP(A25,'04_武器主表'!$A:$I,9,FALSE)*T25,0)</f>
+        <v/>
+      </c>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>完整近身爆发。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_ArcaneBolt</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>760</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>AS 75; CritChance 75; CritPercent 80; Range 90; Knockback 35; Magic 85</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O26" s="2">
+        <f>C26*(D26/100)*(1+E26/100*MAX(0,F26/100-1))</f>
+        <v/>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" s="2">
+        <f>O26*P26*Q26*R26</f>
+        <v/>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" s="2">
+        <f>ROUND(VLOOKUP(A26,'04_武器主表'!$A:$I,9,FALSE)*T26,0)</f>
+        <v/>
+      </c>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>魔法单体入口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_ArcaneBolt</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>AS 78; CritChance 80; CritPercent 85; Range 95; Knockback 35; Magic 95</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O27" s="2">
+        <f>C27*(D27/100)*(1+E27/100*MAX(0,F27/100-1))</f>
+        <v/>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S27" s="2">
+        <f>O27*P27*Q27*R27</f>
+        <v/>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U27" s="2">
+        <f>ROUND(VLOOKUP(A27,'04_武器主表'!$A:$I,9,FALSE)*T27,0)</f>
+        <v/>
+      </c>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>提高攻击和魔法收益。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_ArcaneBolt</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>840</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>AS 82; CritChance 85; CritPercent 90; Range 100; Knockback 40; Magic 110</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O28" s="2">
+        <f>C28*(D28/100)*(1+E28/100*MAX(0,F28/100-1))</f>
+        <v/>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="S28" s="2">
+        <f>O28*P28*Q28*R28</f>
+        <v/>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U28" s="2">
+        <f>ROUND(VLOOKUP(A28,'04_武器主表'!$A:$I,9,FALSE)*T28,0)</f>
+        <v/>
+      </c>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>精准魔法成型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_ArcaneBolt</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>205</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>AS 85; CritChance 90; CritPercent 100; Range 105; Knockback 40; Magic 130</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O29" s="2">
+        <f>C29*(D29/100)*(1+E29/100*MAX(0,F29/100-1))</f>
+        <v/>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="S29" s="2">
+        <f>O29*P29*Q29*R29</f>
+        <v/>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="U29" s="2">
+        <f>ROUND(VLOOKUP(A29,'04_武器主表'!$A:$I,9,FALSE)*T29,0)</f>
+        <v/>
+      </c>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>后期魔法暴击。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_GreatAxe</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>AS 50; CritChance 55; CritPercent 75; Range 85; Knockback 80; Melee 95</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" s="2">
+        <f>C30*(D30/100)*(1+E30/100*MAX(0,F30/100-1))</f>
+        <v/>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S30" s="2">
+        <f>O30*P30*Q30*R30</f>
+        <v/>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" s="2">
+        <f>ROUND(VLOOKUP(A30,'04_武器主表'!$A:$I,9,FALSE)*T30,0)</f>
+        <v/>
+      </c>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>低频大范围。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_GreatAxe</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>AS 52; CritChance 60; CritPercent 80; Range 90; Knockback 85; Melee 110</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O31" s="2">
+        <f>C31*(D31/100)*(1+E31/100*MAX(0,F31/100-1))</f>
+        <v/>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S31" s="2">
+        <f>O31*P31*Q31*R31</f>
+        <v/>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U31" s="2">
+        <f>ROUND(VLOOKUP(A31,'04_武器主表'!$A:$I,9,FALSE)*T31,0)</f>
+        <v/>
+      </c>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>提高基础攻击。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_GreatAxe</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>185</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>AS 55; CritChance 65; CritPercent 85; Range 95; Knockback 90; Melee 130</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O32" s="2">
+        <f>C32*(D32/100)*(1+E32/100*MAX(0,F32/100-1))</f>
+        <v/>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S32" s="2">
+        <f>O32*P32*Q32*R32</f>
+        <v/>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U32" s="2">
+        <f>ROUND(VLOOKUP(A32,'04_武器主表'!$A:$I,9,FALSE)*T32,0)</f>
+        <v/>
+      </c>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>重型成型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Weapon_GreatAxe</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>AS 58; CritChance 70; CritPercent 95; Range 100; Knockback 95; Melee 155</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O33" s="2">
+        <f>C33*(D33/100)*(1+E33/100*MAX(0,F33/100-1))</f>
+        <v/>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S33" s="2">
+        <f>O33*P33*Q33*R33</f>
+        <v/>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="U33" s="2">
+        <f>ROUND(VLOOKUP(A33,'04_武器主表'!$A:$I,9,FALSE)*T33,0)</f>
+        <v/>
+      </c>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>完整高成本重型。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Docs/玩法数值表.xlsx
+++ b/Docs/玩法数值表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AXR_Projects\unity\Survivors\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB14714B-6D59-42F5-B6A3-4E6F1A23A6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB29D78-A0E4-4177-990A-B1B07EB07A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1152" yWindow="1152" windowWidth="23040" windowHeight="12120" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17082,14 +17082,14 @@
         <v>1</v>
       </c>
       <c r="J66" s="2">
-        <f t="shared" ref="J66:J97" si="4">H66*I66</f>
+        <f t="shared" ref="J66:J80" si="4">H66*I66</f>
         <v>160</v>
       </c>
       <c r="K66" s="3">
         <v>150</v>
       </c>
       <c r="L66" s="2">
-        <f t="shared" ref="L66:L97" si="5">J66-K66</f>
+        <f t="shared" ref="L66:L80" si="5">J66-K66</f>
         <v>10</v>
       </c>
       <c r="M66" s="2" t="s">
